--- a/Phím tắt photoshop.xlsx
+++ b/Phím tắt photoshop.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tech\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE50050-DAC5-4C91-BE0B-FCC8943C38CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C173B8D3-7788-4723-BA43-5A85C7FA7D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t xml:space="preserve">alt </t>
   </si>
@@ -87,6 +87,36 @@
   </si>
   <si>
     <t>để lấy thông tin của text</t>
+  </si>
+  <si>
+    <t>Ctrl D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bỏ vùng chọn  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I </t>
+  </si>
+  <si>
+    <t>lấy mã màu</t>
+  </si>
+  <si>
+    <t>Cách xuất hình ảnh</t>
+  </si>
+  <si>
+    <t>vào layer chọn ảnh đó rồi chuột phải chọn quick export as png</t>
+  </si>
+  <si>
+    <t>Cách lấy hình ảnh chuẩn</t>
+  </si>
+  <si>
+    <t>chọn xong thì ctrl alt shift S để lưu</t>
+  </si>
+  <si>
+    <t>back lại file chính bằng history</t>
+  </si>
+  <si>
+    <t>từng hình 1 - crop tool CTRL c , nhiều hình - slice tool ( lúc save chọn all user slice)</t>
   </si>
 </sst>
 </file>
@@ -404,13 +434,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="7" max="7" width="21.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -421,7 +451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="G2" t="s">
         <v>14</v>
       </c>
@@ -429,7 +459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="G3" t="s">
         <v>3</v>
       </c>
@@ -437,7 +467,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="G4" t="s">
         <v>4</v>
       </c>
@@ -445,7 +475,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="G5" t="s">
         <v>7</v>
       </c>
@@ -453,7 +483,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="G6" t="s">
         <v>9</v>
       </c>
@@ -461,7 +491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="G7" t="s">
         <v>12</v>
       </c>
@@ -469,12 +499,52 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="G8" t="s">
         <v>15</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="G9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="G14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
